--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,131 @@
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>订单类型</t>
+  </si>
+  <si>
+    <t>对账状态</t>
+  </si>
+  <si>
+    <t>物流渠道</t>
+  </si>
+  <si>
+    <t>物流单号</t>
+  </si>
+  <si>
+    <t>运输状态</t>
+  </si>
+  <si>
+    <t>实重</t>
+  </si>
+  <si>
+    <t>体积重</t>
+  </si>
+  <si>
+    <t>计费重</t>
+  </si>
+  <si>
+    <t>预估运费</t>
+  </si>
+  <si>
+    <t>计费重[物流商]</t>
+  </si>
+  <si>
+    <t>实际运费[物流商]</t>
+  </si>
+  <si>
+    <t>运费差异</t>
+  </si>
+  <si>
+    <t>平台</t>
+  </si>
+  <si>
+    <t>店铺/客户</t>
+  </si>
+  <si>
+    <t>订单号</t>
+  </si>
+  <si>
+    <t>出库单号</t>
+  </si>
+  <si>
+    <t>目的国家</t>
+  </si>
+  <si>
+    <t>下单时间</t>
+  </si>
+  <si>
+    <t>发货时间</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>{.sourceTypeName}</t>
+  </si>
+  <si>
+    <t>{.reconciliationStatusName}</t>
+  </si>
+  <si>
+    <t>{.channelName}</t>
+  </si>
+  <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
+    <t>{.transportStatusName}</t>
+  </si>
+  <si>
+    <t>{.actualWeight}</t>
+  </si>
+  <si>
+    <t>{.volumeWeight}</t>
+  </si>
+  <si>
+    <t>{.billingWeight}</t>
+  </si>
+  <si>
+    <t>{.estimatedShippingCost}</t>
+  </si>
+  <si>
+    <t>{.billingWeightLogistics}</t>
+  </si>
+  <si>
+    <t>{.actualShippingCost}</t>
+  </si>
+  <si>
+    <t>{.diffShippingCost}</t>
+  </si>
+  <si>
+    <t>{.salesPlatform}</t>
+  </si>
+  <si>
+    <t>{.customerName}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.outstockCode}</t>
+  </si>
+  <si>
+    <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.orderTime}</t>
+  </si>
+  <si>
+    <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,9 +1066,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="14.25" customWidth="1"/>
+    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="11" max="11" width="20.75" customWidth="1"/>
+    <col min="12" max="12" width="12.375" customWidth="1"/>
+    <col min="13" max="13" width="16.5" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15.75" customWidth="1"/>
+    <col min="16" max="16" width="13.875" customWidth="1"/>
+    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="18" max="19" width="13.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
@@ -11,7 +11,20 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -78,7 +91,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>{.sourceTypeName}</t>
+    <t>{.orderTypeName}</t>
   </si>
   <si>
     <t>{.reconciliationStatusName}</t>
@@ -141,7 +154,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>订单类型</t>
   </si>
@@ -64,6 +64,12 @@
     <t>实际运费[物流商]</t>
   </si>
   <si>
+    <t>实际报关费</t>
+  </si>
+  <si>
+    <t>实际其他费用</t>
+  </si>
+  <si>
     <t>运费差异</t>
   </si>
   <si>
@@ -122,6 +128,12 @@
   </si>
   <si>
     <t>{.actualShippingCost}</t>
+  </si>
+  <si>
+    <t>{.actualDeclareCost}</t>
+  </si>
+  <si>
+    <t>{.actualOtherCost}</t>
   </si>
   <si>
     <t>{.diffShippingCost}</t>
@@ -1079,7 +1091,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1092,17 +1104,17 @@
     <col min="8" max="8" width="12.375" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
     <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="11" width="20.75" customWidth="1"/>
-    <col min="12" max="12" width="12.375" customWidth="1"/>
-    <col min="13" max="13" width="16.5" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="15.75" customWidth="1"/>
-    <col min="16" max="16" width="13.875" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
-    <col min="18" max="19" width="13.125" customWidth="1"/>
+    <col min="11" max="13" width="20.75" customWidth="1"/>
+    <col min="14" max="14" width="17.125" customWidth="1"/>
+    <col min="15" max="15" width="16.5" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="15.75" customWidth="1"/>
+    <col min="18" max="18" width="13.875" customWidth="1"/>
+    <col min="19" max="19" width="13.75" customWidth="1"/>
+    <col min="20" max="21" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1163,67 +1175,79 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
@@ -40,7 +40,7 @@
     <t>物流渠道</t>
   </si>
   <si>
-    <t>物流单号</t>
+    <t>物流跟踪单号</t>
   </si>
   <si>
     <t>运输状态</t>
@@ -106,7 +106,7 @@
     <t>{.channelName}</t>
   </si>
   <si>
-    <t>{.transportNo}</t>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.transportStatusName}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
@@ -151,7 +151,7 @@
     <t>{.customerName}</t>
   </si>
   <si>
-    <t>{.chargeName}</t>
+    <t>{.shopChargeName}</t>
   </si>
   <si>
     <t>{.platformCode}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>订单类型</t>
   </si>
@@ -58,6 +58,12 @@
     <t>预估运费</t>
   </si>
   <si>
+    <t>预估报关费用</t>
+  </si>
+  <si>
+    <t>预估其他费用</t>
+  </si>
+  <si>
     <t>计费重[物流商]</t>
   </si>
   <si>
@@ -100,6 +106,12 @@
     <t>发货时间</t>
   </si>
   <si>
+    <t>计费规则</t>
+  </si>
+  <si>
+    <t>账单确认时间</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -130,6 +142,12 @@
     <t>{.estimatedShippingCost}</t>
   </si>
   <si>
+    <t>{.estimatedDeclareCost}</t>
+  </si>
+  <si>
+    <t>{.estimatedOtherCost}</t>
+  </si>
+  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
@@ -170,6 +188,12 @@
   </si>
   <si>
     <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.feeRuleName}</t>
+  </si>
+  <si>
+    <t>{.confirmTime}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -179,11 +203,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -788,8 +813,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1103,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1114,20 +1142,20 @@
     <col min="6" max="6" width="13.25" customWidth="1"/>
     <col min="7" max="7" width="16.375" customWidth="1"/>
     <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="13" width="20.75" customWidth="1"/>
-    <col min="14" max="14" width="16.75" customWidth="1"/>
-    <col min="15" max="15" width="16.5" customWidth="1"/>
-    <col min="16" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="18.25" customWidth="1"/>
-    <col min="19" max="19" width="15.75" customWidth="1"/>
-    <col min="20" max="20" width="13.875" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="23" width="13.125" customWidth="1"/>
+    <col min="9" max="11" width="14.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.125" customWidth="1"/>
+    <col min="13" max="15" width="20.75" customWidth="1"/>
+    <col min="16" max="16" width="16.75" customWidth="1"/>
+    <col min="17" max="17" width="16.5" customWidth="1"/>
+    <col min="18" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="18.25" customWidth="1"/>
+    <col min="21" max="21" width="15.75" customWidth="1"/>
+    <col min="22" max="22" width="13.875" customWidth="1"/>
+    <col min="23" max="23" width="13.75" customWidth="1"/>
+    <col min="24" max="27" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1152,13 +1180,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1200,79 +1228,103 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
